--- a/Bai1.1_TestCase.xlsx
+++ b/Bai1.1_TestCase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\Software-Testing\Buoi7\1150080143_VoAnhKiet_CNPM2_Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D291818F-A551-406C-B803-3066C9C47BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8768252F-BDD1-4CE5-951E-CAEF9837D6A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -135,9 +135,6 @@
   </si>
   <si>
     <t>Các bước thực hiện</t>
-  </si>
-  <si>
-    <t>KIỂM THỬ LOGIC ĐĂNG KÝ</t>
   </si>
   <si>
     <t>TC08</t>
@@ -714,6 +711,9 @@
   <si>
     <t>B1: Không tích chọn Điều khoản
 B2: Nút Đăng ký (Disabled)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIỂM THỬ </t>
   </si>
 </sst>
 </file>
@@ -912,26 +912,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1232,14 +1232,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20.399999999999999">
-      <c r="A1" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="A1" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="6"/>
@@ -1256,16 +1256,16 @@
         <v>27</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="D3" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
@@ -1332,17 +1332,17 @@
       <c r="I7" s="6"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="23" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="22" t="s">
         <v>30</v>
       </c>
       <c r="F8" s="6"/>
@@ -1355,14 +1355,14 @@
         <v>1</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="5">
         <v>1</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -1374,14 +1374,14 @@
         <v>2</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="5">
         <v>2</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
@@ -1393,14 +1393,14 @@
         <v>3</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="5">
         <v>3</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
@@ -1421,7 +1421,7 @@
     <row r="13" spans="1:9">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -1434,7 +1434,7 @@
     <row r="14" spans="1:9">
       <c r="A14" s="3"/>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -1447,7 +1447,7 @@
     <row r="15" spans="1:9">
       <c r="A15" s="3"/>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -1460,7 +1460,7 @@
     <row r="16" spans="1:9">
       <c r="A16" s="3"/>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -1473,7 +1473,7 @@
     <row r="17" spans="1:9" s="12" customFormat="1">
       <c r="A17" s="19"/>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C17" s="19"/>
       <c r="D17" s="19"/>
@@ -1482,7 +1482,7 @@
     <row r="18" spans="1:9">
       <c r="A18" s="8"/>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
@@ -1509,10 +1509,10 @@
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="20" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1521,15 +1521,15 @@
         <v>3</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="46.8">
       <c r="A23" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1544,91 +1544,91 @@
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="26" t="s">
+      <c r="C27" s="24" t="s">
         <v>54</v>
-      </c>
-      <c r="C27" s="26" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="31.2">
       <c r="A28" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="C28" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="46.8">
       <c r="A29" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:9" s="12" customFormat="1" ht="31.2">
       <c r="A30" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="C30" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="12" customFormat="1" ht="31.2">
       <c r="A31" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:9" s="12" customFormat="1" ht="31.2">
       <c r="A32" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="12" customFormat="1">
       <c r="A33" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="C33" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="12" customFormat="1">
       <c r="A34" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="C34" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1641,217 +1641,217 @@
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="26" t="s">
+      <c r="A37" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="B37" s="26" t="s">
+      <c r="C37" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="C37" s="26" t="s">
+      <c r="D37" s="24" t="s">
         <v>79</v>
-      </c>
-      <c r="D37" s="26" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="C38" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="D38" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="5"/>
       <c r="B39" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="D39" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="5"/>
       <c r="B40" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>89</v>
-      </c>
       <c r="D40" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="5"/>
       <c r="B41" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>91</v>
-      </c>
       <c r="D41" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="12" customFormat="1">
       <c r="A42" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>93</v>
-      </c>
       <c r="D42" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="12" customFormat="1">
       <c r="A43" s="5"/>
       <c r="B43" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="12" customFormat="1">
       <c r="A44" s="5"/>
       <c r="B44" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="12" customFormat="1">
       <c r="A45" s="5"/>
       <c r="B45" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="12" customFormat="1">
       <c r="A46" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>98</v>
-      </c>
       <c r="D46" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="12" customFormat="1">
       <c r="A47" s="5"/>
       <c r="B47" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="12" customFormat="1">
       <c r="A48" s="5"/>
       <c r="B48" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:5" s="12" customFormat="1">
       <c r="A49" s="5"/>
       <c r="B49" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="1:5" s="12" customFormat="1">
       <c r="A50" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C50" s="5" t="s">
+      <c r="D50" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:5" s="12" customFormat="1">
       <c r="A51" s="5"/>
       <c r="B51" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:5" s="12" customFormat="1">
       <c r="A52" s="5"/>
       <c r="B52" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="D52" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:5" s="12" customFormat="1">
       <c r="A53" s="5"/>
       <c r="B53" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1887,16 +1887,16 @@
         <v>11</v>
       </c>
       <c r="B58" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="D58" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="E58" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="31.2">
@@ -1904,16 +1904,16 @@
         <v>12</v>
       </c>
       <c r="B59" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="D59" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E59" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="31.2">
@@ -1921,16 +1921,16 @@
         <v>13</v>
       </c>
       <c r="B60" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C60" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="D60" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E60" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="31.2">
@@ -1938,16 +1938,16 @@
         <v>14</v>
       </c>
       <c r="B61" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C61" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="D61" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E61" s="5" t="s">
         <v>120</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1955,16 +1955,16 @@
         <v>15</v>
       </c>
       <c r="B62" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="D62" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="E62" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1972,16 +1972,16 @@
         <v>16</v>
       </c>
       <c r="B63" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C63" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="D63" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D63" s="5" t="s">
-        <v>128</v>
-      </c>
       <c r="E63" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1989,254 +1989,254 @@
         <v>17</v>
       </c>
       <c r="B64" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C64" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="D64" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="E64" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="65" spans="1:5" s="12" customFormat="1" ht="31.2">
       <c r="A65" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B65" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="D65" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D65" s="5" t="s">
+      <c r="E65" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="66" spans="1:5" s="12" customFormat="1">
       <c r="A66" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B66" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="D66" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D66" s="5" t="s">
+      <c r="E66" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="67" spans="1:5" s="12" customFormat="1">
       <c r="A67" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B67" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C67" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="D67" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D67" s="5" t="s">
+      <c r="E67" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="68" spans="1:5" s="12" customFormat="1">
       <c r="A68" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B68" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="C68" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="D68" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D68" s="5" t="s">
+      <c r="E68" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="69" spans="1:5" s="12" customFormat="1">
       <c r="A69" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B69" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="C69" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="D69" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D69" s="5" t="s">
+      <c r="E69" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="70" spans="1:5" s="12" customFormat="1">
       <c r="A70" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B70" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="C70" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="C70" s="5" t="s">
+      <c r="D70" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D70" s="5" t="s">
+      <c r="E70" s="5" t="s">
         <v>158</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="71" spans="1:5" s="12" customFormat="1">
       <c r="A71" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B71" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="C71" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="D71" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="D71" s="5" t="s">
+      <c r="E71" s="5" t="s">
         <v>163</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="72" spans="1:5" s="12" customFormat="1">
       <c r="A72" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B72" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="C72" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="D72" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D72" s="5" t="s">
+      <c r="E72" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="73" spans="1:5" s="12" customFormat="1">
       <c r="A73" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B73" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="C73" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C73" s="5" t="s">
+      <c r="D73" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="D73" s="5" t="s">
+      <c r="E73" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:5" s="12" customFormat="1">
       <c r="A74" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B74" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="C74" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="D74" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D74" s="5" t="s">
+      <c r="E74" s="5" t="s">
         <v>178</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="75" spans="1:5" s="12" customFormat="1">
       <c r="A75" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B75" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="B75" s="5" t="s">
+      <c r="C75" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="C75" s="5" t="s">
+      <c r="D75" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="D75" s="5" t="s">
+      <c r="E75" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="76" spans="1:5" s="12" customFormat="1" ht="31.2">
       <c r="A76" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B76" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="C76" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="D76" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="D76" s="5" t="s">
+      <c r="E76" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="77" spans="1:5" s="12" customFormat="1" ht="31.2">
       <c r="A77" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B77" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="C77" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="D77" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E77" s="5" t="s">
         <v>192</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B78" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="C78" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="C78" s="5" t="s">
+      <c r="D78" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="D78" s="5" t="s">
+      <c r="E78" s="5" t="s">
         <v>197</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="80" spans="1:5">
